--- a/diseases/d172/2000-2004.xlsx
+++ b/diseases/d172/2000-2004.xlsx
@@ -776,6 +776,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO2" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -924,6 +929,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO3" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1072,6 +1082,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO4" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1220,6 +1235,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO5" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1368,6 +1388,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO6" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1516,6 +1541,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO7" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1664,6 +1694,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO8" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1812,6 +1847,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO9" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -1960,6 +2000,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO10" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2108,6 +2153,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO11" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2256,6 +2306,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO12" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2404,6 +2459,11 @@
           <t>wpp_computed</t>
         </is>
       </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>monthly</t>
+        </is>
+      </c>
       <c r="AO13" t="inlineStr">
         <is>
           <t>legacy_fallback</t>
@@ -2550,6 +2610,11 @@
       <c r="S14" t="inlineStr">
         <is>
           <t>wpp_computed</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>monthly</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">

--- a/diseases/d172/2000-2004.xlsx
+++ b/diseases/d172/2000-2004.xlsx
@@ -771,11 +771,6 @@
       <c r="R2" t="n">
         <v>0.02647355736154732</v>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -788,23 +783,13 @@
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr"/>
       <c r="AT2" t="n">
         <v>0</v>
       </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV2" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -924,11 +909,6 @@
       <c r="R3" t="n">
         <v>0.01323677868077366</v>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -941,23 +921,13 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="n">
         <v>0</v>
       </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV3" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1077,11 +1047,6 @@
       <c r="R4" t="n">
         <v>0.004412259560257887</v>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1094,23 +1059,13 @@
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr"/>
       <c r="AT4" t="n">
         <v>0</v>
       </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV4" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1230,11 +1185,6 @@
       <c r="R5" t="n">
         <v>0.008824519120515774</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1247,23 +1197,13 @@
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr"/>
       <c r="AT5" t="n">
         <v>0</v>
       </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV5" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1383,11 +1323,6 @@
       <c r="R6" t="n">
         <v>0.01764903824103155</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1400,23 +1335,13 @@
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr"/>
       <c r="AT6" t="n">
         <v>0</v>
       </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV6" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1536,11 +1461,6 @@
       <c r="R7" t="n">
         <v>0.01758594945947606</v>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1553,23 +1473,13 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr"/>
       <c r="AT7" t="n">
         <v>0</v>
       </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV7" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1689,11 +1599,6 @@
       <c r="R8" t="n">
         <v>0.01318946209460705</v>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1706,23 +1611,13 @@
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr"/>
       <c r="AT8" t="n">
         <v>0</v>
       </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV8" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1842,11 +1737,6 @@
       <c r="R9" t="n">
         <v>0.008792974729738031</v>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -1859,23 +1749,13 @@
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr"/>
       <c r="AT9" t="n">
         <v>0</v>
       </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV9" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -1995,11 +1875,6 @@
       <c r="R10" t="n">
         <v>0.008792974729738031</v>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2012,23 +1887,13 @@
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr"/>
       <c r="AT10" t="n">
         <v>0</v>
       </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV10" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2148,11 +2013,6 @@
       <c r="R11" t="n">
         <v>0.004396487364869015</v>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2165,23 +2025,13 @@
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr"/>
       <c r="AT11" t="n">
         <v>0</v>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV11" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2301,11 +2151,6 @@
       <c r="R12" t="n">
         <v>0.008792974729738031</v>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2318,23 +2163,13 @@
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr"/>
       <c r="AT12" t="n">
         <v>0</v>
       </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV12" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2454,11 +2289,6 @@
       <c r="R13" t="n">
         <v>0.004396487364869015</v>
       </c>
-      <c r="S13" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2471,23 +2301,13 @@
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr"/>
       <c r="AT13" t="n">
         <v>0</v>
       </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
-      </c>
       <c r="AV13" t="inlineStr">
         <is>
           <t>nidss_open_data</t>
@@ -2607,11 +2427,6 @@
       <c r="R14" t="n">
         <v>0.01758594945947606</v>
       </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>wpp_computed</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>monthly</t>
@@ -2624,22 +2439,12 @@
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>legacy_fallback</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>legacy_identity_may_be_lossy</t>
+          <t>published_series</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr"/>
       <c r="AT14" t="n">
         <v>0</v>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>No eligible registered case-count series facts are available for this disease and country; the public curve uses the legacy flat table.</t>
-        </is>
       </c>
       <c r="AV14" t="inlineStr">
         <is>
